--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-patient-education.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-patient-education.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T12:47:35+00:00</t>
+    <t>2026-05-07T13:30:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-ML-Sections/ig/StructureDefinition-fr-lm-patient-education.xlsx
+++ b/htr-ML-Sections/ig/StructureDefinition-fr-lm-patient-education.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Modèle logique métier - FR LM Patient Education</t>
+    <t>Logical model - FR LM Patient Education</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T13:30:39+00:00</t>
+    <t>2026-05-12T13:21:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -375,7 +375,7 @@
     <t>fr-lm-section.entry</t>
   </si>
   <si>
-    <t>fr-lm-patient-education.entry.acte</t>
+    <t>fr-lm-patient-education.entry.procedure</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure
@@ -398,11 +398,11 @@
     <t>fr-lm-patient-education.entry.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-references-externes
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-attachment
 </t>
   </si>
   <si>
-    <t>Entrée References externes</t>
+    <t>Entrée Références externes</t>
   </si>
 </sst>
 </file>
@@ -717,7 +717,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
